--- a/Recipe sheet workbook format.xlsx
+++ b/Recipe sheet workbook format.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\GitHub\reactor_pressure_data_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Desktop\GitHub\reactor_pressure_data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5457DB9-019A-44E2-AFA8-9D8587659762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C72221D-DEC7-4C6A-91A9-3FB078E9FC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{539505D8-28CE-4AF5-B1B8-D9A0288D63DA}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{539505D8-28CE-4AF5-B1B8-D9A0288D63DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Recipe sheet (page 1)" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>Info</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Purge</t>
   </si>
   <si>
-    <t>In order for this workbook to function as a recipe sheet, this worksheet must be the first sheet of the book and columns A:I must remain strictly dedicated to the recipe sheet information</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -150,6 +147,32 @@
   </si>
   <si>
     <t>SiO2</t>
+  </si>
+  <si>
+    <t>Reactor Companion App</t>
+  </si>
+  <si>
+    <t>Recipe Sheet (PRE-RUN ONLY)</t>
+  </si>
+  <si>
+    <t>1. Use **Recipe sheet workbook format.xlsx** as the starting template, save a copy, and do not insert, delete, or reorder columns or rows in the A–J recipe area.
+2. Fill in the metadata rows above **Cycles**. Keep each zone’s **Valve/precursor**, **Name**, and **Temperature (C)** values in the same column; use `nan` only when a value is not applicable. Any valve used in the timing table must have a numeric valve number declared above.
+3. In the timing table, enter a cycle count only on the first row of each sequence, enter a valve number on every row, and enter all timing values in seconds. Use `0` for unused timing phases; do not leave required values blank.</t>
+  </si>
+  <si>
+    <t>1. Use this area to perform calculations such as time estimation, record notes mid run, and keep a log of changes made to the recipe mid run. This is also a good place to record iSE data while a GPC curve is being generated on the ISR, especially if multiple runs are used sequentially. 
+2. If changes are made to the recipe mid run, you should wait until the end of the process to modify the header of the raw data file. 
+3. In the gui, under reactor plots, select the raw data JSON, open Edit Header and then mannually make changes so that the header reflects the process as it was performed. It's important to note that doing this requires careful thought about how to accurately represent the correct header information. Its best to wait until after a complete cycle has completed before changing the recipe in order to avoid half-correct cycle recipes. After making the neccessary changes, make sure "Also save changes to the header text file" and press save. 
+4. Alternatively, highlight the modifications and add a note to the modified rows to indicate the mid run modification before copying the correct recipe into rows A-J, then select "Regenerate header from recipe sheet" in the Edit Header menu. This will automatically load the header, with your corrections, into the menu for you to save and overwrite the incorrect header data in the raw data file(s)</t>
+  </si>
+  <si>
+    <t>Calculations and mid run notes and changes to the recipe, as well as iSE data</t>
+  </si>
+  <si>
+    <t>The rest of the worksheet / workbook can be used to record post run notes and data such as iSE data and analysis, exposure and leak rate information, cycle plots, etc.</t>
+  </si>
+  <si>
+    <t>Post-run notes and data -&gt;</t>
   </si>
 </sst>
 </file>
@@ -161,7 +184,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="mm/dd/yy\ h:mm\ AM/PM"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,6 +319,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -478,7 +517,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -611,6 +650,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -656,19 +732,56 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -725,10 +838,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1048,343 +1157,377 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456AF080-381C-4412-8C71-8F493E8A8FF3}">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:AG26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="4"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="3"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="16.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="3" customWidth="1"/>
+    <col min="16" max="19" width="9.140625" style="3"/>
+    <col min="20" max="20" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:33" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
+    </row>
+    <row r="2" spans="1:33" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="18"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+      <c r="AB2" s="20"/>
+      <c r="AC2" s="20"/>
+      <c r="AD2" s="20"/>
+    </row>
+    <row r="3" spans="1:33" ht="270" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="3"/>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="B1" t="s">
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6"/>
+      <c r="L6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" s="3">
+        <f>SUM(C15:I26)*A15</f>
+        <v>61620</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>18.53</v>
+      </c>
+      <c r="R6" s="5"/>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="7">
+        <v>46239</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="R7" s="5"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>137</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="7">
+        <f ca="1">NOW()+M6/3600/24</f>
+        <v>46320.145308217587</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9">
+        <v>12</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" s="3">
+        <v>18.53</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>60</v>
+      </c>
+      <c r="D11">
+        <v>50</v>
+      </c>
+      <c r="E11">
+        <v>40</v>
+      </c>
+      <c r="F11">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="3">
+        <v>4.93</v>
+      </c>
+      <c r="P11" s="3">
+        <v>2.3370920000000002</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0.44405899999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="M12" s="8"/>
+      <c r="P12" s="3">
+        <v>28.316841</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>4.9262079999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="M13" s="9"/>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3">
-        <f>SUM(C12:I23)*A12</f>
-        <v>61620</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3">
-        <v>18.53</v>
-      </c>
-      <c r="R3" s="5"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="7">
-        <v>46239</v>
-      </c>
-      <c r="N4" s="5"/>
-      <c r="R4" s="5"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>137</v>
-      </c>
-      <c r="L5" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="7">
-        <f ca="1">NOW()+M3/3600/24</f>
-        <v>46239.536869560179</v>
-      </c>
-      <c r="P5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6">
+      <c r="B14">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" t="s">
-        <v>37</v>
-      </c>
-      <c r="P6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M7">
-        <v>18.53</v>
-      </c>
-      <c r="P7" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>100</v>
-      </c>
-      <c r="C8">
-        <v>60</v>
-      </c>
-      <c r="D8">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8">
-        <v>4.93</v>
-      </c>
-      <c r="P8">
-        <v>2.3370920000000002</v>
-      </c>
-      <c r="Q8">
-        <v>0.44405899999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="M9" s="2"/>
-      <c r="P9">
-        <v>28.316841</v>
-      </c>
-      <c r="Q9">
-        <v>4.9262079999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>1</v>
-      </c>
-      <c r="B11">
-        <v>7</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
         <v>15</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>20</v>
-      </c>
-      <c r="B12">
-        <v>5</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>60</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B13">
-        <v>8</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>60</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B14">
-        <v>12</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
       <c r="E14">
         <v>0</v>
       </c>
@@ -1392,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1401,21 +1544,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>20</v>
+      </c>
       <c r="B15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1424,15 +1570,12 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>20</v>
-      </c>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -1447,7 +1590,7 @@
         <v>60</v>
       </c>
       <c r="G16">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1458,7 +1601,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C17">
         <v>4</v>
@@ -1470,27 +1613,27 @@
         <v>0</v>
       </c>
       <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
         <v>60</v>
       </c>
-      <c r="G17">
-        <v>300</v>
-      </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>150</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B18">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1499,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1509,37 +1652,37 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>20</v>
+      </c>
       <c r="B19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>20</v>
-      </c>
       <c r="B20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -1560,12 +1703,12 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>300</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -1577,27 +1720,27 @@
         <v>0</v>
       </c>
       <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
         <v>60</v>
       </c>
-      <c r="G21">
-        <v>300</v>
-      </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>300</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B22">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1606,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1616,44 +1759,136 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>20</v>
+      </c>
       <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>60</v>
+      </c>
+      <c r="G23">
+        <v>300</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>60</v>
+      </c>
+      <c r="G24">
+        <v>300</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>12</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>60</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B26">
         <v>7</v>
       </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
         <v>15</v>
       </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
         <v>10</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="K2:T2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="K3:T3"/>
+    <mergeCell ref="U2:AD2"/>
+    <mergeCell ref="U3:AD3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8524c750-d52a-4243-9720-728bc70efb7c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="60d5a4fa-dfb8-4032-a39f-c398b36dd0e4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1846,20 +2081,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8524c750-d52a-4243-9720-728bc70efb7c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="60d5a4fa-dfb8-4032-a39f-c398b36dd0e4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010FBDC9-D7DE-46DA-94AB-5E18B7FC2084}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{105801AB-C7A2-453F-BAA2-8972793E6FDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8524c750-d52a-4243-9720-728bc70efb7c"/>
+    <ds:schemaRef ds:uri="60d5a4fa-dfb8-4032-a39f-c398b36dd0e4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1884,12 +2120,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{105801AB-C7A2-453F-BAA2-8972793E6FDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010FBDC9-D7DE-46DA-94AB-5E18B7FC2084}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8524c750-d52a-4243-9720-728bc70efb7c"/>
-    <ds:schemaRef ds:uri="60d5a4fa-dfb8-4032-a39f-c398b36dd0e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
